--- a/SmartSearch/qna/MART_SmartSearch_QnA_Log_v1.1_20260817_en.xlsx
+++ b/SmartSearch/qna/MART_SmartSearch_QnA_Log_v1.1_20260817_en.xlsx
@@ -3402,7 +3402,7 @@
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
@@ -3420,8 +3420,16 @@
           <t>19/08/2026</t>
         </is>
       </c>
-      <c r="K58" s="11" t="n"/>
-      <c r="L58" s="11" t="n"/>
+      <c r="K58" s="11" t="inlineStr">
+        <is>
+          <t>Resolved per the 2026-08-24 BA meeting (new supplementary priority rule #5): the official ranking criterion is the COUNT OF QUERY WORDS MATCHED against the product (most word matches ranks first) - this is a NEW ranking criterion standing alongside/above the existing tier system, NOT merely a same-tier tie-break. This confirms the BRD FR-SP-01 interpretation (counting matches in the product name), NOT the Storyboard SS-SCR-002 "search volume" interpretation. Test case SS-SCR-002-SC1-TC3 (written per the Storyboard) needs re-review. See new test cases SS-SCR-005-SC11-TC1 and INT-01-SC3-TC1.</t>
+        </is>
+      </c>
+      <c r="L58" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -4055,7 +4063,7 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>INT-01-SC1-TC1 (Out-of-stock override) still has clear BRD backing and is unaffected. INT-01-SC1-TC2 ('Business rule &gt; pure Relevance') is testing an order assumption with NO BASIS — if the real mechanism is a single blended formula (no discrete tiers), TC2 is fundamentally wrong and needs to be rewritten.</t>
+          <t>INT-01-SC1-TC1 (Out-of-stock override) still has clear BRD backing and is unaffected. INT-01-SC1-TC2 ('Business rule &gt; pure Relevance') is testing an order assumption with NO BASIS — if the real mechanism is a single blended formula (no discrete tiers), TC2 is fundamentally wrong and needs to be rewritten. [Update 2026-08-24: rule 5 (BA meeting) confirms "most word matches" as a NEW ranking criterion standing alongside/above the tier system - does NOT directly resolve the 4-tier order question above, but BA/TD still need to confirm this new criterion's relative position within the overall priority chain. See INT-01-SC3-TC1.]</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -4109,7 +4117,7 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>INT-01-SC2-TC1 can only verify CONSISTENCY across repeated calls (no random reshuffling) — it cannot be scored Pass/Fail against a specific expected order until the official secondary criterion is known.</t>
+          <t>INT-01-SC2-TC1 can only verify CONSISTENCY across repeated calls (no random reshuffling) — it cannot be scored Pass/Fail against a specific expected order until the official secondary criterion is known. [Update 2026-08-24: rule 5 confirms matchedWords (count of matched query words) as a newly-confirmed ranking criterion by BA - could serve as part of the secondary criterion for exactly-equal Scorecard scores, but is NOT sufficient alone to close this QnA since matchedWords' position relative to other secondary criteria (Product_ID, update time, sales volume...) is still unclear. See INT-01-SC3-TC1.]</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -4179,6 +4187,60 @@
       <c r="K72" s="11" t="n"/>
       <c r="L72" s="11" t="n"/>
     </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>QnA-69</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>Search Result / Zero-Result — the field defining "Active" for the Elasticsearch display rule (rule 2, BA meeting 2026-08-24) is not yet formally confirmed by BA/Dev</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>The 2026-08-24 BA meeting confirmed the rule: "the OpenSearch system works together with Elasticsearch to decide which products show in Search result and autocomplete (Elasticsearch only shows products that are Active)" — but did NOT specify which exact field defines "Active". In the real catalogue data (ProductInfo) there are at least 4 candidate fields, each producing a different exclusion set: `status` (Magento catalog status, 1=Enabled/2=Disabled - excludes 208/16340 SKUs), `ec_status` (0/1), `visibility_search` (bool - false on 63 SKUs), `visibility_catalog` (bool - false on 2453 SKUs). The current simulated test-data engine TEMPORARILY uses `status`, per the stakeholder's explicit instruction, pending confirmation. Need BA/Dev to confirm the official field (possibly one field, or a combination) that defines "Active" for Search/Autocomplete display purposes.</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>BA meeting 2026-08-24, rule 2 (no formal REQ ID yet) - related to SS-SCR-005-SC12-TC1, INT-09-SC5-TC1</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>QC (reviewing the new rule from the 2026-08-24 BA meeting)</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>BA / Dev</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC12-TC1 and INT-09-SC5-TC1 are currently tested against the temporary `status` field - may be WRONG and need re-review if the official field turns out to be ec_status/visibility_search/visibility_catalog or a combination.</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC12-TC1, INT-09-SC5-TC1</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="n"/>
+      <c r="L73" s="11" t="n"/>
+    </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
@@ -4186,7 +4248,7 @@
         </is>
       </c>
       <c r="B74" s="12">
-        <f>COUNTA(A5:A72)</f>
+        <f>COUNTA(A5:A73)</f>
         <v/>
       </c>
     </row>
